--- a/artfynd/A 37041-2024 artfynd.xlsx
+++ b/artfynd/A 37041-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120111585</v>
+        <v>120111413</v>
       </c>
       <c r="B2" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398232</v>
+        <v>398264</v>
       </c>
       <c r="R2" t="n">
-        <v>6698052</v>
+        <v>6698053</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120111495</v>
+        <v>120111423</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398252</v>
+        <v>398277</v>
       </c>
       <c r="R3" t="n">
-        <v>6698049</v>
+        <v>6698055</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120111413</v>
+        <v>120111585</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>398264</v>
+        <v>398232</v>
       </c>
       <c r="R5" t="n">
-        <v>6698053</v>
+        <v>6698052</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120111423</v>
+        <v>120111495</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,21 +1108,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>398277</v>
+        <v>398252</v>
       </c>
       <c r="R6" t="n">
-        <v>6698055</v>
+        <v>6698049</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 37041-2024 artfynd.xlsx
+++ b/artfynd/A 37041-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120111423</v>
+        <v>120111375</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398277</v>
+        <v>398246</v>
       </c>
       <c r="R3" t="n">
-        <v>6698055</v>
+        <v>6698098</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120111375</v>
+        <v>120111585</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,47 +900,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398246</v>
+        <v>398232</v>
       </c>
       <c r="R4" t="n">
-        <v>6698098</v>
+        <v>6698052</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120111585</v>
+        <v>120111423</v>
       </c>
       <c r="B5" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>398232</v>
+        <v>398277</v>
       </c>
       <c r="R5" t="n">
-        <v>6698052</v>
+        <v>6698055</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 37041-2024 artfynd.xlsx
+++ b/artfynd/A 37041-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120111413</v>
+        <v>120111423</v>
       </c>
       <c r="B2" t="n">
         <v>78526</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398264</v>
+        <v>398277</v>
       </c>
       <c r="R2" t="n">
-        <v>6698053</v>
+        <v>6698055</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120111375</v>
+        <v>120111495</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,47 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398246</v>
+        <v>398252</v>
       </c>
       <c r="R3" t="n">
-        <v>6698098</v>
+        <v>6698049</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -990,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120111423</v>
+        <v>120111413</v>
       </c>
       <c r="B5" t="n">
         <v>78526</v>
@@ -1030,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>398277</v>
+        <v>398264</v>
       </c>
       <c r="R5" t="n">
-        <v>6698055</v>
+        <v>6698053</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120111495</v>
+        <v>120111375</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,38 +1095,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>398252</v>
+        <v>398246</v>
       </c>
       <c r="R6" t="n">
-        <v>6698049</v>
+        <v>6698098</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 37041-2024 artfynd.xlsx
+++ b/artfynd/A 37041-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120111423</v>
+        <v>120111413</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398277</v>
+        <v>398264</v>
       </c>
       <c r="R2" t="n">
-        <v>6698055</v>
+        <v>6698053</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
         <v>120111495</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>120111585</v>
       </c>
       <c r="B4" t="n">
-        <v>90527</v>
+        <v>90545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120111413</v>
+        <v>120111375</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>398264</v>
+        <v>398246</v>
       </c>
       <c r="R5" t="n">
-        <v>6698053</v>
+        <v>6698098</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120111375</v>
+        <v>120111423</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,47 +1104,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>398246</v>
+        <v>398277</v>
       </c>
       <c r="R6" t="n">
-        <v>6698098</v>
+        <v>6698055</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 37041-2024 artfynd.xlsx
+++ b/artfynd/A 37041-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120111413</v>
+        <v>120111375</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398264</v>
+        <v>398246</v>
       </c>
       <c r="R2" t="n">
-        <v>6698053</v>
+        <v>6698098</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120111495</v>
+        <v>120111413</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398252</v>
+        <v>398264</v>
       </c>
       <c r="R3" t="n">
-        <v>6698049</v>
+        <v>6698053</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120111585</v>
+        <v>120111495</v>
       </c>
       <c r="B4" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398232</v>
+        <v>398252</v>
       </c>
       <c r="R4" t="n">
-        <v>6698052</v>
+        <v>6698049</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120111375</v>
+        <v>120111423</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,47 +1002,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>398246</v>
+        <v>398277</v>
       </c>
       <c r="R5" t="n">
-        <v>6698098</v>
+        <v>6698055</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120111423</v>
+        <v>120111585</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>398277</v>
+        <v>398232</v>
       </c>
       <c r="R6" t="n">
-        <v>6698055</v>
+        <v>6698052</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 37041-2024 artfynd.xlsx
+++ b/artfynd/A 37041-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120111375</v>
+        <v>120111495</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398246</v>
+        <v>398252</v>
       </c>
       <c r="R2" t="n">
-        <v>6698098</v>
+        <v>6698049</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120111413</v>
+        <v>120111375</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +789,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398264</v>
+        <v>398246</v>
       </c>
       <c r="R3" t="n">
-        <v>6698053</v>
+        <v>6698098</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120111495</v>
+        <v>120111423</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398252</v>
+        <v>398277</v>
       </c>
       <c r="R4" t="n">
-        <v>6698049</v>
+        <v>6698055</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120111423</v>
+        <v>120111585</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>398277</v>
+        <v>398232</v>
       </c>
       <c r="R5" t="n">
-        <v>6698055</v>
+        <v>6698052</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120111585</v>
+        <v>120111413</v>
       </c>
       <c r="B6" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>398232</v>
+        <v>398264</v>
       </c>
       <c r="R6" t="n">
-        <v>6698052</v>
+        <v>6698053</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 37041-2024 artfynd.xlsx
+++ b/artfynd/A 37041-2024 artfynd.xlsx
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120111423</v>
+        <v>120111585</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398277</v>
+        <v>398232</v>
       </c>
       <c r="R4" t="n">
-        <v>6698055</v>
+        <v>6698052</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120111585</v>
+        <v>120111423</v>
       </c>
       <c r="B5" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>398232</v>
+        <v>398277</v>
       </c>
       <c r="R5" t="n">
-        <v>6698052</v>
+        <v>6698055</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 37041-2024 artfynd.xlsx
+++ b/artfynd/A 37041-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120111495</v>
+        <v>120111585</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398252</v>
+        <v>398232</v>
       </c>
       <c r="R2" t="n">
-        <v>6698049</v>
+        <v>6698052</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120111375</v>
+        <v>120111423</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,47 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398246</v>
+        <v>398277</v>
       </c>
       <c r="R3" t="n">
-        <v>6698098</v>
+        <v>6698055</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120111585</v>
+        <v>120111413</v>
       </c>
       <c r="B4" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398232</v>
+        <v>398264</v>
       </c>
       <c r="R4" t="n">
-        <v>6698052</v>
+        <v>6698053</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120111423</v>
+        <v>120111375</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,38 +993,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>398277</v>
+        <v>398246</v>
       </c>
       <c r="R5" t="n">
-        <v>6698055</v>
+        <v>6698098</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120111413</v>
+        <v>120111495</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,21 +1108,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>398264</v>
+        <v>398252</v>
       </c>
       <c r="R6" t="n">
-        <v>6698053</v>
+        <v>6698049</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 37041-2024 artfynd.xlsx
+++ b/artfynd/A 37041-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120111585</v>
+        <v>120111413</v>
       </c>
       <c r="B2" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398232</v>
+        <v>398264</v>
       </c>
       <c r="R2" t="n">
-        <v>6698052</v>
+        <v>6698053</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120111423</v>
+        <v>120111495</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398277</v>
+        <v>398252</v>
       </c>
       <c r="R3" t="n">
-        <v>6698055</v>
+        <v>6698049</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120111413</v>
+        <v>120111423</v>
       </c>
       <c r="B4" t="n">
         <v>78542</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398264</v>
+        <v>398277</v>
       </c>
       <c r="R4" t="n">
-        <v>6698053</v>
+        <v>6698055</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120111375</v>
+        <v>120111585</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,47 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>398246</v>
+        <v>398232</v>
       </c>
       <c r="R5" t="n">
-        <v>6698098</v>
+        <v>6698052</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120111495</v>
+        <v>120111375</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,38 +1095,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>398252</v>
+        <v>398246</v>
       </c>
       <c r="R6" t="n">
-        <v>6698049</v>
+        <v>6698098</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 37041-2024 artfynd.xlsx
+++ b/artfynd/A 37041-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120111495</v>
+        <v>120111375</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398252</v>
+        <v>398246</v>
       </c>
       <c r="R3" t="n">
-        <v>6698049</v>
+        <v>6698098</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120111423</v>
+        <v>120111585</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398277</v>
+        <v>398232</v>
       </c>
       <c r="R4" t="n">
-        <v>6698055</v>
+        <v>6698052</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120111585</v>
+        <v>120111423</v>
       </c>
       <c r="B5" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>398232</v>
+        <v>398277</v>
       </c>
       <c r="R5" t="n">
-        <v>6698052</v>
+        <v>6698055</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120111375</v>
+        <v>120111495</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,47 +1104,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kullåsmyren med omnejd, Kullåsmyren med omnejd, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>398246</v>
+        <v>398252</v>
       </c>
       <c r="R6" t="n">
-        <v>6698098</v>
+        <v>6698049</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
